--- a/order_forms/046_swimming_pool_construction_intake_form--order_forms.xlsx
+++ b/order_forms/046_swimming_pool_construction_intake_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -914,17 +914,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pool_type_choices</t>
+          <t>pool_size_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>in-ground_pools_(spas)</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>In-Ground Pools (Spas)</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -953,29 +953,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pool_size_choices</t>
+          <t>pool_shape_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>rectangular</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Rectangular</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rectangular</t>
+          <t>freeform</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rectangular</t>
+          <t>Freeform</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>freeform</t>
+          <t>kidney-shaped</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Freeform</t>
+          <t>Kidney-Shaped</t>
         </is>
       </c>
     </row>
@@ -1021,29 +1021,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>kidney-shaped</t>
+          <t>infinity_pools</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kidney-Shaped</t>
+          <t>Infinity Pools</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pool_shape_choices</t>
+          <t>pool_color_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>infinity_pools</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Infinity Pools</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>black</t>
+          <t>gray</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Gray</t>
         </is>
       </c>
     </row>
@@ -1106,29 +1106,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gray</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pool_color_choices</t>
+          <t>pool_features_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>spas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Spas</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>spas</t>
+          <t>tanning_decks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spas</t>
+          <t>Tanning Decks</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tanning_decks</t>
+          <t>waterfalls</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tanning Decks</t>
+          <t>Waterfalls</t>
         </is>
       </c>
     </row>
@@ -1174,29 +1174,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>waterfalls</t>
+          <t>waterfalls_and_tanning_decks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Waterfalls</t>
+          <t>Waterfalls and Tanning Decks</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pool_features_choices</t>
+          <t>pool_contact_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>waterfalls_and_tanning_decks</t>
+          <t>landline</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Waterfalls and Tanning Decks</t>
+          <t>Landline</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>landline</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Landline</t>
+          <t>Cell</t>
         </is>
       </c>
     </row>
@@ -1225,29 +1225,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pool_contact_choices</t>
+          <t>contractor_contact_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>landline</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Landline</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>landline</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Landline</t>
+          <t>Cell</t>
         </is>
       </c>
     </row>
@@ -1276,29 +1276,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>cell</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>contractor_contact_choices</t>
+          <t>project_status_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1327,27 +1327,10 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>on_hold</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
-        <is>
-          <t>On Hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>project_status_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
         <is>
           <t>Cancelled</t>
         </is>
